--- a/Indicators/Sugar-sweetened beverages.xlsx
+++ b/Indicators/Sugar-sweetened beverages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uredu.sharepoint.com/sites/ControlTabacoFacultadEconomica/Documentos compartidos/Monitoreo/Bebidas azucaradas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uredu.sharepoint.com/sites/ControlTabacoFacultadEconomica/Documentos compartidos/Monitoreo/Repositorio/Indicators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{5BD938E4-EBA6-4B7D-8170-4BF3A8B18242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CACD846F-777B-4241-A99D-8AF6F8B6C59A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{5BD938E4-EBA6-4B7D-8170-4BF3A8B18242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{842ECC3D-0C5C-42E9-9059-C407E1FBE435}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8269B95E-4A31-4A95-9BD6-389467BE89FF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8269B95E-4A31-4A95-9BD6-389467BE89FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Gasto alimentos ultraprocesados" sheetId="2" r:id="rId1"/>
@@ -1338,10 +1338,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$A$2:$A$9</c:f>
+              <c:f>'Prevalencias y consumo'!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2016</c:v>
                 </c:pt>
@@ -1365,16 +1365,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$B$2:$B$9</c:f>
+              <c:f>'Prevalencias y consumo'!$B$2:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="4">
                   <c:v>2.5099999999999998</c:v>
                 </c:pt>
@@ -1386,6 +1389,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2.86</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1495,10 +1501,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$A$2:$A$9</c:f>
+              <c:f>'Prevalencias y consumo'!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2016</c:v>
                 </c:pt>
@@ -1522,16 +1528,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$C$2:$C$9</c:f>
+              <c:f>'Prevalencias y consumo'!$C$2:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>4.28</c:v>
                 </c:pt>
@@ -1555,6 +1564,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3.23</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1954,10 +1966,10 @@
           </c:errBars>
           <c:cat>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$A$2:$A$9</c:f>
+              <c:f>'Prevalencias y consumo'!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2016</c:v>
                 </c:pt>
@@ -1981,16 +1993,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$D$2:$D$9</c:f>
+              <c:f>'Prevalencias y consumo'!$D$2:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>71.509999999999991</c:v>
                 </c:pt>
@@ -2014,6 +2029,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>67.17</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>64.599999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2142,10 +2160,10 @@
           </c:errBars>
           <c:cat>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$A$2:$A$9</c:f>
+              <c:f>'Prevalencias y consumo'!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2016</c:v>
                 </c:pt>
@@ -2169,16 +2187,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Prevalencias y consumo'!$G$2:$G$9</c:f>
+              <c:f>'Prevalencias y consumo'!$G$2:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="4" formatCode="0.00">
                   <c:v>48.1</c:v>
                 </c:pt>
@@ -2190,6 +2211,9 @@
                 </c:pt>
                 <c:pt idx="7" formatCode="0.00">
                   <c:v>54.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5786,15 +5810,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>762001</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>170448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1163053</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>1921243</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>66175</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5825,15 +5849,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1672063</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>189941</xdr:rowOff>
+      <xdr:colOff>356711</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>170391</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1266787</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>146539</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2020666</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>134608</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5903,10 +5927,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6227,15 +6247,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5938F424-B750-4FB4-8D86-19053BC5C3B9}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="6" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="6" width="30.109375" customWidth="1"/>
     <col min="7" max="7" width="29" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6256,7 +6276,7 @@
       </c>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -6278,7 +6298,7 @@
         <v>1.7217851725445583</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -6300,7 +6320,7 @@
         <v>2.0068216497621401</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2022</v>
       </c>
@@ -6322,7 +6342,7 @@
         <v>2.8051217963976831</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -6330,7 +6350,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G7" s="1"/>
     </row>
   </sheetData>
@@ -6342,16 +6362,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A3C958-9AFF-44F6-8515-10936390DC9E}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="7" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="7" width="30.109375" customWidth="1"/>
     <col min="8" max="8" width="29" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" customWidth="1"/>
+    <col min="9" max="9" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6380,7 +6400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -6401,7 +6421,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -6416,12 +6436,12 @@
         <v>0.24128369999999999</v>
       </c>
       <c r="F3" s="11">
-        <f t="shared" ref="F3:F9" si="0">E3*F$11</f>
+        <f t="shared" ref="F3:F10" si="0">E3*F$11</f>
         <v>0.47291605199999998</v>
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -6441,7 +6461,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -6460,7 +6480,7 @@
         <v>0.17381279999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -6493,7 +6513,7 @@
         <v>0.19213135199999998</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -6526,7 +6546,7 @@
         <v>0.19572168000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -6560,7 +6580,7 @@
         <v>0.19788199200000001</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -6594,7 +6614,38 @@
         <v>0.20152857199999999</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10">
+        <v>2.75</v>
+      </c>
+      <c r="C10">
+        <v>3.11</v>
+      </c>
+      <c r="D10">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.19796</v>
+      </c>
+      <c r="G10">
+        <v>50.57</v>
+      </c>
+      <c r="H10">
+        <v>0.105</v>
+      </c>
+      <c r="I10">
+        <f>H10*1.96</f>
+        <v>0.20579999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F11">
         <v>1.96</v>
       </c>
@@ -6608,12 +6659,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C9BF31-BA8C-423F-9765-3B79A73455D5}">
   <dimension ref="A1:D127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -6627,7 +6678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2014</v>
       </c>
@@ -6641,7 +6692,7 @@
         <v>85.97</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -6655,7 +6706,7 @@
         <v>86.29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2014</v>
       </c>
@@ -6669,7 +6720,7 @@
         <v>86.08</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2014</v>
       </c>
@@ -6683,7 +6734,7 @@
         <v>85.89</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -6697,7 +6748,7 @@
         <v>86.09</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2014</v>
       </c>
@@ -6711,7 +6762,7 @@
         <v>86.48</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2014</v>
       </c>
@@ -6725,7 +6776,7 @@
         <v>86.73</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2014</v>
       </c>
@@ -6739,7 +6790,7 @@
         <v>86.63</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2014</v>
       </c>
@@ -6753,7 +6804,7 @@
         <v>86.71</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2014</v>
       </c>
@@ -6767,7 +6818,7 @@
         <v>86.83</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2014</v>
       </c>
@@ -6781,7 +6832,7 @@
         <v>86.81</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2014</v>
       </c>
@@ -6795,7 +6846,7 @@
         <v>87.02</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2015</v>
       </c>
@@ -6809,7 +6860,7 @@
         <v>87.22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2015</v>
       </c>
@@ -6823,7 +6874,7 @@
         <v>87.46</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2015</v>
       </c>
@@ -6837,7 +6888,7 @@
         <v>87.57</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2015</v>
       </c>
@@ -6851,7 +6902,7 @@
         <v>87.33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2015</v>
       </c>
@@ -6865,7 +6916,7 @@
         <v>87.93</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2015</v>
       </c>
@@ -6879,7 +6930,7 @@
         <v>88.06</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2015</v>
       </c>
@@ -6893,7 +6944,7 @@
         <v>87.7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2015</v>
       </c>
@@ -6907,7 +6958,7 @@
         <v>87.85</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2015</v>
       </c>
@@ -6921,7 +6972,7 @@
         <v>88.2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2015</v>
       </c>
@@ -6935,7 +6986,7 @@
         <v>87.87</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2015</v>
       </c>
@@ -6949,7 +7000,7 @@
         <v>87.86</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2015</v>
       </c>
@@ -6963,7 +7014,7 @@
         <v>88.04</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2016</v>
       </c>
@@ -6977,7 +7028,7 @@
         <v>88.77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2016</v>
       </c>
@@ -6991,7 +7042,7 @@
         <v>89.77</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2016</v>
       </c>
@@ -7005,7 +7056,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2016</v>
       </c>
@@ -7019,7 +7070,7 @@
         <v>91.63</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2016</v>
       </c>
@@ -7033,7 +7084,7 @@
         <v>91.66</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2016</v>
       </c>
@@ -7047,7 +7098,7 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2016</v>
       </c>
@@ -7061,7 +7112,7 @@
         <v>91.19</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2016</v>
       </c>
@@ -7075,7 +7126,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2016</v>
       </c>
@@ -7089,7 +7140,7 @@
         <v>92.47</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2016</v>
       </c>
@@ -7103,7 +7154,7 @@
         <v>92.51</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2016</v>
       </c>
@@ -7117,7 +7168,7 @@
         <v>93.03</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2016</v>
       </c>
@@ -7131,7 +7182,7 @@
         <v>94.37</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2017</v>
       </c>
@@ -7145,7 +7196,7 @@
         <v>95.27</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2017</v>
       </c>
@@ -7159,7 +7210,7 @@
         <v>96.46</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2017</v>
       </c>
@@ -7173,7 +7224,7 @@
         <v>96.4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2017</v>
       </c>
@@ -7187,7 +7238,7 @@
         <v>96.07</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2017</v>
       </c>
@@ -7201,7 +7252,7 @@
         <v>96.19</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2017</v>
       </c>
@@ -7215,7 +7266,7 @@
         <v>96.08</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2017</v>
       </c>
@@ -7229,7 +7280,7 @@
         <v>96.37</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2017</v>
       </c>
@@ -7243,7 +7294,7 @@
         <v>96.35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2017</v>
       </c>
@@ -7257,7 +7308,7 @@
         <v>96.63</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2017</v>
       </c>
@@ -7271,7 +7322,7 @@
         <v>97.28</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2017</v>
       </c>
@@ -7285,7 +7336,7 @@
         <v>97.36</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2017</v>
       </c>
@@ -7299,7 +7350,7 @@
         <v>97.73</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2018</v>
       </c>
@@ -7313,7 +7364,7 @@
         <v>98.24</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2018</v>
       </c>
@@ -7327,7 +7378,7 @@
         <v>98.29</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2018</v>
       </c>
@@ -7341,7 +7392,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2018</v>
       </c>
@@ -7355,7 +7406,7 @@
         <v>98.84</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2018</v>
       </c>
@@ -7369,7 +7420,7 @@
         <v>99.78</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2018</v>
       </c>
@@ -7383,7 +7434,7 @@
         <v>99.25</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2018</v>
       </c>
@@ -7397,7 +7448,7 @@
         <v>99.05</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2018</v>
       </c>
@@ -7411,7 +7462,7 @@
         <v>99.26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2018</v>
       </c>
@@ -7425,7 +7476,7 @@
         <v>99.27</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2018</v>
       </c>
@@ -7439,7 +7490,7 @@
         <v>99.32</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2018</v>
       </c>
@@ -7453,7 +7504,7 @@
         <v>99.63</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2018</v>
       </c>
@@ -7467,7 +7518,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2019</v>
       </c>
@@ -7481,7 +7532,7 @@
         <v>102.6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2019</v>
       </c>
@@ -7495,7 +7546,7 @@
         <v>103.25</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2019</v>
       </c>
@@ -7509,7 +7560,7 @@
         <v>104.9</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2019</v>
       </c>
@@ -7523,7 +7574,7 @@
         <v>105.76</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2019</v>
       </c>
@@ -7537,7 +7588,7 @@
         <v>106.98</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2019</v>
       </c>
@@ -7551,7 +7602,7 @@
         <v>106.95</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2019</v>
       </c>
@@ -7565,7 +7616,7 @@
         <v>106.98</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2019</v>
       </c>
@@ -7579,7 +7630,7 @@
         <v>106.83</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2019</v>
       </c>
@@ -7593,7 +7644,7 @@
         <v>107.74</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2019</v>
       </c>
@@ -7607,7 +7658,7 @@
         <v>107.9</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2019</v>
       </c>
@@ -7621,7 +7672,7 @@
         <v>107.86</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2019</v>
       </c>
@@ -7635,7 +7686,7 @@
         <v>108.15</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2020</v>
       </c>
@@ -7649,7 +7700,7 @@
         <v>108.67</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2020</v>
       </c>
@@ -7663,7 +7714,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2020</v>
       </c>
@@ -7677,7 +7728,7 @@
         <v>109.37</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2020</v>
       </c>
@@ -7691,7 +7742,7 @@
         <v>110.26</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2020</v>
       </c>
@@ -7705,7 +7756,7 @@
         <v>110.45</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2020</v>
       </c>
@@ -7719,7 +7770,7 @@
         <v>110.82</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2020</v>
       </c>
@@ -7733,7 +7784,7 @@
         <v>111.1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2020</v>
       </c>
@@ -7747,7 +7798,7 @@
         <v>111.52</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2020</v>
       </c>
@@ -7761,7 +7812,7 @@
         <v>111.54</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2020</v>
       </c>
@@ -7775,7 +7826,7 @@
         <v>111.31</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>2020</v>
       </c>
@@ -7789,7 +7840,7 @@
         <v>111.69</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2020</v>
       </c>
@@ -7803,7 +7854,7 @@
         <v>111.35</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2021</v>
       </c>
@@ -7817,7 +7868,7 @@
         <v>111.41</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2021</v>
       </c>
@@ -7831,7 +7882,7 @@
         <v>111.46</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2021</v>
       </c>
@@ -7845,7 +7896,7 @@
         <v>111.85</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2021</v>
       </c>
@@ -7859,7 +7910,7 @@
         <v>113.64</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2021</v>
       </c>
@@ -7873,7 +7924,7 @@
         <v>114.46</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2021</v>
       </c>
@@ -7887,7 +7938,7 @@
         <v>114.81</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2021</v>
       </c>
@@ -7901,7 +7952,7 @@
         <v>115.36</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2021</v>
       </c>
@@ -7915,7 +7966,7 @@
         <v>115.99</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2021</v>
       </c>
@@ -7929,7 +7980,7 @@
         <v>116.51</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2021</v>
       </c>
@@ -7943,7 +7994,7 @@
         <v>116.95</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2021</v>
       </c>
@@ -7957,7 +8008,7 @@
         <v>118.1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2021</v>
       </c>
@@ -7971,7 +8022,7 @@
         <v>118.53</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2022</v>
       </c>
@@ -7985,7 +8036,7 @@
         <v>119.61</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2022</v>
       </c>
@@ -7999,7 +8050,7 @@
         <v>122.93</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2022</v>
       </c>
@@ -8013,7 +8064,7 @@
         <v>126.66</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2022</v>
       </c>
@@ -8027,7 +8078,7 @@
         <v>129.75</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2022</v>
       </c>
@@ -8041,7 +8092,7 @@
         <v>131.13999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2022</v>
       </c>
@@ -8055,7 +8106,7 @@
         <v>132.63</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2022</v>
       </c>
@@ -8069,7 +8120,7 @@
         <v>133.96</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2022</v>
       </c>
@@ -8083,7 +8134,7 @@
         <v>135.81</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2022</v>
       </c>
@@ -8097,7 +8148,7 @@
         <v>141.44</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2022</v>
       </c>
@@ -8111,7 +8162,7 @@
         <v>142.72</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2022</v>
       </c>
@@ -8125,7 +8176,7 @@
         <v>145.36000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2022</v>
       </c>
@@ -8139,7 +8190,7 @@
         <v>147.11000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2023</v>
       </c>
@@ -8153,7 +8204,7 @@
         <v>149.01</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2023</v>
       </c>
@@ -8167,7 +8218,7 @@
         <v>152.32</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2023</v>
       </c>
@@ -8181,7 +8232,7 @@
         <v>154.38</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2023</v>
       </c>
@@ -8195,7 +8246,7 @@
         <v>154.65</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2023</v>
       </c>
@@ -8209,7 +8260,7 @@
         <v>154.93</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2023</v>
       </c>
@@ -8223,7 +8274,7 @@
         <v>154.75</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2023</v>
       </c>
@@ -8237,7 +8288,7 @@
         <v>156.36000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2023</v>
       </c>
@@ -8251,7 +8302,7 @@
         <v>158.19999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2023</v>
       </c>
@@ -8265,7 +8316,7 @@
         <v>159.19</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2023</v>
       </c>
@@ -8279,7 +8330,7 @@
         <v>159.54</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2023</v>
       </c>
@@ -8293,7 +8344,7 @@
         <v>164.79</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2023</v>
       </c>
@@ -8307,7 +8358,7 @@
         <v>167.21</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2024</v>
       </c>
@@ -8321,7 +8372,7 @@
         <v>169.25</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2024</v>
       </c>
@@ -8335,7 +8386,7 @@
         <v>170.34</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2024</v>
       </c>
@@ -8349,7 +8400,7 @@
         <v>169.79</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2024</v>
       </c>
@@ -8363,7 +8414,7 @@
         <v>168.38</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2024</v>
       </c>
@@ -8377,7 +8428,7 @@
         <v>169.46</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2024</v>
       </c>
@@ -8398,26 +8449,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027EAE559E09D4A429EBD0F39DC21BBA6" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c9719185c29a5bbeaf569b57ce7223ff">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57ed4d19-7dfa-4218-b0c9-321a76363151" xmlns:ns3="f52a8275-2cbd-4186-978c-53e036657375" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6164b0d521ef8826ab87409b1a303be5" ns2:_="" ns3:_="">
     <xsd:import namespace="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
@@ -8660,10 +8691,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57ed4d19-7dfa-4218-b0c9-321a76363151">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f52a8275-2cbd-4186-978c-53e036657375" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4670C963-F52E-47C3-BE4C-E31F74B9F034}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1E36F3-F225-4557-836A-77F664833080}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
+    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8680,20 +8742,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1E36F3-F225-4557-836A-77F664833080}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4670C963-F52E-47C3-BE4C-E31F74B9F034}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="57ed4d19-7dfa-4218-b0c9-321a76363151"/>
-    <ds:schemaRef ds:uri="f52a8275-2cbd-4186-978c-53e036657375"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>